--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573189805</v>
+        <v>46157.93113550645</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113550645</v>
+        <v>46157.93180695432</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93180695432</v>
+        <v>46157.93404624409</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93404624409</v>
+        <v>46157.93722679446</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93722679446</v>
+        <v>46158.28220567388</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28220567388</v>
+        <v>46158.296971576</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.296971576</v>
+        <v>46158.29820070501</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820070501</v>
+        <v>46158.33391539926</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391539926</v>
+        <v>46158.36861359946</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/найти/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861359946</v>
+        <v>46158.37291990031</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
